--- a/daily_matches/job_matches_2026-06-06.xlsx
+++ b/daily_matches/job_matches_2026-06-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Developer (Contractor) RITM1788244</t>
+          <t>Sr Data Engineer- Data Platform &amp; AI Enablement</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RE/SPEC Inc</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.7</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, OpenCV, YOLO, MLflow, Docker</t>
+          <t>Data Scientist, Generative AI, RAG, Redshift, CI/CD, Git, Snowflake, Redshift, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13c5ed8137da59b7</t>
+          <t>https://www.indeed.com/viewjob?jk=18c6ead6041dd8b2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (DevOps)</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ActiveProspect, Inc.</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, PostgreSQL, MySQL</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Redshift, Docker, Kubernetes, Terraform, Git, Redshift</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a17efe4f6a851376</t>
+          <t>https://www.indeed.com/viewjob?jk=e22d14682cc7c157</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (API Integrations)</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Kinesis, Docker, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Redshift, Docker, Kubernetes, Terraform, Git, Redshift</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b03d7c92e1f21c5</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6a02642c276bf4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI/ML Engineer (Senior Associate) - Remote</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, FastAPI, Docker, CI/CD</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Redshift, Docker, Kubernetes, Terraform, Git, Redshift</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af9b8b8d54273bfc</t>
+          <t>https://www.indeed.com/viewjob?jk=70afb87e4855ee97</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>imgIX</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Gemini, FastAPI, PostgreSQL, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Redshift, Docker, Kubernetes, Terraform, Git, Redshift</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a1f424451beb52</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4478af45a9bae5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Software Development</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Green Dot Corporation</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Redshift, Docker, Kubernetes, Terraform, Git, Redshift</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d2cee654e77a926</t>
+          <t>https://www.indeed.com/viewjob?jk=a4d17985a6e35637</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Engineer 2, Software Development</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Green Dot Corporation</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Redshift, Docker, Kubernetes, Terraform, Git, Redshift</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcfe2fccf97c19b8</t>
+          <t>https://www.indeed.com/viewjob?jk=b5a2598e1734a29f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data &amp; Analytics (AI)</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Palm Tree</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala, Optimization, A/B Testing</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Redshift, Docker, Kubernetes, Terraform, Git, Redshift</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c89a4a908e9bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=731dfd555cf56cb1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Expedient</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>17.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, FastAPI, Kubernetes, Python, SQL, R, Java</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Redshift, Docker, Kubernetes, Terraform, Git, Redshift</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a93cfd38e6b3a098</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c97680def5315c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer, GTM AI - Python</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Telnyx</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>17.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Python, SQL, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Redshift, Docker, Kubernetes, Terraform, Git, Redshift</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a95463e809865774</t>
+          <t>https://www.indeed.com/viewjob?jk=96784c2186363543</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Specialist - Software Engineering</t>
+          <t>Engineering - Agentic AI Engineer (Junior)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Aline</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>17.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Kafka, MongoDB, SQL, R, Java</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Redshift, Docker, Kubernetes, Terraform, Git, Redshift</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9320ff724eaa96e8</t>
+          <t>https://www.indeed.com/viewjob?jk=d109e7ef208735a6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Search Data and Systems Engineer, Organic and Agentic Search</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Autodesk</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Snowflake, BigQuery, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, RAG, Gemini, Copilot, BigQuery, Dataflow, Kubernetes, CI/CD, Git, BigQuery</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c3f12eab1b8545</t>
+          <t>https://www.indeed.com/viewjob?jk=5db37bdf41206f3d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Machine Learning Platform Engineer</t>
+          <t>Senior Specialist - AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, Python, R, Scala, Optimization</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cff298d88dba8e73</t>
+          <t>https://www.indeed.com/viewjob?jk=08373e49d792c0ca</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Machine Learning Platform Engineer</t>
+          <t>Software Engineer, AI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Patch My PC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, Python, R, Scala, Optimization</t>
+          <t>Generative AI, LangChain, RAG, Mistral, Hugging Face, Prompt Engineering, Docker, CI/CD, Git, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14ede44f8eea5e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=05fd2b9f3d1f55b1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Machine Learning Platform Engineer</t>
+          <t>Associate - AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, Python, R, Scala, Optimization</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,19 +986,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a415125d66770ec</t>
+          <t>https://www.indeed.com/viewjob?jk=8d31dbbc0fb39329</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Machine Learning Platform Engineer</t>
+          <t>Senior Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, Python, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Prompt Engineering, Kubernetes, CI/CD, Jenkins, Git, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,19 +1021,19 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc24c6aa785bf837</t>
+          <t>https://www.indeed.com/viewjob?jk=26482741958a217b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Research Engineer, Olmo + Molmo</t>
+          <t>Senior Software Engineer, Cloud Platform</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Allen Institute for Artificial Intelligence</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, AKS, Python, R, Scala</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e754d524d50990e</t>
+          <t>https://www.indeed.com/viewjob?jk=6653c38b7c76bc19</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>HR -Data Scientist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java, Scala</t>
+          <t>Data Scientist, RAG, MLflow, CI/CD, Terraform, Git, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29bdb2a80bdb83c4</t>
+          <t>https://www.indeed.com/viewjob?jk=6a457b4897928b47</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior AI Engineer (*3-Year LTE)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, R, Scala</t>
+          <t>AI Engineer, RAG, Hugging Face, Prompt Engineering, PyTorch, Docker, CI/CD, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdccde5177523430</t>
+          <t>https://www.indeed.com/viewjob?jk=a696b244f763a9d5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Core Team - San Jose, CA</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ZEDEDA</t>
+          <t>New York Blood Center</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Rye, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>LangChain, Docker, Kubernetes, Kafka, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e397b047701e84a7</t>
+          <t>https://www.indeed.com/viewjob?jk=558c0c0c483e56c0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>South Florida Community Care Network</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, CI/CD, Python</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e85663babe35c1bf</t>
+          <t>https://www.indeed.com/viewjob?jk=c162c1d6e8c68b2e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>.NET Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Zocalo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=342ec1f3ac47cc5a</t>
+          <t>https://www.indeed.com/viewjob?jk=be44f927a6b4d174</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Dev Ops</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Loveland Innovations</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Pleasant Grove, UT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd38faa46bda24aa</t>
+          <t>https://www.indeed.com/viewjob?jk=a2ad44b08aa08c7e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Backend Java Engineer - Post Trade Accounting, Associate</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Snowflake, Kafka, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f6310fafac695db</t>
+          <t>https://www.indeed.com/viewjob?jk=1a70a6a9d580d712</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer in Test II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Aliso Viejo, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e346dab87c3fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=dee68ed71eaf15db</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer in Test II</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eb4595dcbfcf65e</t>
+          <t>https://www.indeed.com/viewjob?jk=659b5903b2ccd88d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer (Backend)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, S3, Glue, Docker, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc440b03d50152cc</t>
+          <t>https://www.indeed.com/viewjob?jk=d0c7e73e30de23d3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Distinguished Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Redshift, BigQuery, Kinesis, Snowflake, BigQuery, Redshift, Kafka, SQL, R</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,42 +1441,357 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c658785d86fc686</t>
+          <t>https://www.indeed.com/viewjob?jk=25ec3ffd343b6320</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AWS SME</t>
+          <t>Data Bricks Migration and Support engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Epathusa</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Databricks, PySpark, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f646314becd0f4e</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Data Bricks Migration and Support engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Databricks, PySpark, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be6dc96e2f68af48</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AWS DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Lake Mary, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Docker, Kubernetes, Jenkins, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e9d8f7febdbb9f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AWS DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Gilbert, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Docker, Kubernetes, Jenkins, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8861e0e658a2ea3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AWS DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Mechanicsburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Docker, Kubernetes, Jenkins, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b90bffda4e84f5e</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Software Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CoorsTek</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Golden, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Kubernetes, CI/CD, Terraform, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=088f92fa01dbe0cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Healthcare Data Analyst, Analytics Hub</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ECG Management Consultants</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e0a9c5b60f0fa8d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Sr Software Development Engineer in Test (Sr SDET)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PlayStation</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Aliso Viejo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>10</v>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, Docker, CI/CD, Terraform, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e0b0d616a1c3096</t>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8186f7c65cfcfcd5</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Software Developer – Healthcare Analytics &amp; AI</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, Git, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed975a86424a7516</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, AKS, Terraform, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3e516bbdb62c7a8</t>
         </is>
       </c>
     </row>
